--- a/Implementation doc/Mikes_stories.xlsx
+++ b/Implementation doc/Mikes_stories.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a43712/Desktop/MA.NorwegianBasin/Implementation doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA031C93-BCAC-074F-B54C-7C9D439ACCFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F931697F-C9E6-C54D-BC2C-194C9CA7001C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" activeTab="1" xr2:uid="{42E5A92F-267B-4B69-9450-AB0ABF14FAF6}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" activeTab="1" xr2:uid="{42E5A92F-267B-4B69-9450-AB0ABF14FAF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Tourist1" sheetId="1" r:id="rId1"/>
@@ -551,7 +551,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -670,10 +670,6 @@
     <xf numFmtId="3" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2368,13 +2364,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4579D33F-77C7-4CB2-BF6A-4CC354C354D6}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="7" max="7" width="10" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="92" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="92" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>77</v>
       </c>
@@ -2390,12 +2383,8 @@
       <c r="E1" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="G1" s="40">
-        <f>34/52</f>
-        <v>0.65384615384615385</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>6</v>
       </c>
@@ -2412,9 +2401,8 @@
         <f>0.7843*B2</f>
         <v>1243.8997999999999</v>
       </c>
-      <c r="G2" s="41"/>
-    </row>
-    <row r="3" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>7</v>
       </c>
@@ -2432,7 +2420,7 @@
         <v>90.272929999999988</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>8</v>
       </c>
@@ -2450,7 +2438,7 @@
         <v>647.20436000000007</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>9</v>
       </c>
@@ -2468,7 +2456,7 @@
         <v>63.606729999999992</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>10</v>
       </c>
@@ -2486,7 +2474,7 @@
         <v>62.508710000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>11</v>
       </c>
@@ -2504,7 +2492,7 @@
         <v>10.66648</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>12</v>
       </c>
@@ -2522,7 +2510,7 @@
         <v>53.724550000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>13</v>
       </c>
@@ -2540,7 +2528,7 @@
         <v>136.23291</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>14</v>
       </c>
@@ -2558,7 +2546,7 @@
         <v>11.999790000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="27" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>15</v>
       </c>
@@ -2576,7 +2564,7 @@
         <v>2320.1162599999998</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="53" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="53" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>16</v>
       </c>
@@ -2594,7 +2582,7 @@
         <v>2309.4497799999999</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="53" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" ht="53" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>17</v>
       </c>
@@ -2612,7 +2600,7 @@
         <v>1.8566204287515764</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="40" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" ht="40" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
         <v>18</v>
       </c>
